--- a/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
+++ b/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
@@ -205,7 +205,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:12 ACST</t>
+          <t>2026-05-04 07:11:43 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -245,17 +245,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.0499</t>
+          <t>-0.0421</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-0.1247</t>
+          <t>-0.1072</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -280,17 +280,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-0.0878</t>
+          <t>-0.0794</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>-0.2986</t>
+          <t>-0.2779</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -392,7 +392,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:12 ACST</t>
+          <t>2026-05-04 07:11:43 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:12 ACST</t>
+          <t>2026-05-04 07:11:43 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>flashscore:GOQASy66</t>
+          <t>flashscore:zs3PZaZa</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -599,152 +599,152 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Mirandes</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.3097</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t/>
+          <t>2.4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t/>
+          <t>-0.107</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t/>
+          <t>-0.2567</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t/>
+          <t>pass</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2084</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t/>
+          <t>3.4</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t/>
+          <t>-0.0857</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t/>
+          <t>-0.2914</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t/>
+          <t>pass</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.4819</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t/>
+          <t>2.88</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.3879</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2063</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t/>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t/>
+          <t>bet</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t/>
+          <t>away</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t/>
+          <t>bet</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t/>
+          <t>2.88</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.4819</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t/>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t/>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -754,29 +754,29 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>bet</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Phase 4 status was upstream_blocked.</t>
+          <t>Bet recommended; subject to portfolio cap.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:12 ACST</t>
+          <t>2026-05-04 07:11:43 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>flashscore:zs3PZaZa</t>
+          <t>flashscore:rTwrFuZR</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -791,347 +791,160 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.3097</t>
+          <t>0.2111</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.107</t>
+          <t>0.0573</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-0.2567</t>
+          <t>0.3722</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>0.0677</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>16.93</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0.2192</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0.0018</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0.0083</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.0023</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.5697</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>-0.1247</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>-0.1796</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0.2084</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>-0.0857</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>-0.2914</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0.4819</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0.3879</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0.2063</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>bet</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0.2111</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0.0573</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>16.93</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>bet</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0.4819</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
       <c r="AK5" t="inlineStr">
-        <is>
-          <t>Bet recommended; subject to portfolio cap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-05-04 06:57:12 ACST</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>flashscore:rTwrFuZR</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.2111</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.0573</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0.3722</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>0.0677</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>16.93</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0.2192</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>4.6</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0.0018</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0.0083</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0.0023</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0.5697</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>-0.1247</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>-0.1796</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0.2111</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>0.0573</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>16.93</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
         <is>
           <t>Bet recommended; subject to portfolio cap.</t>
         </is>
@@ -1334,7 +1147,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:12 ACST</t>
+          <t>2026-05-04 07:11:43 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1374,17 +1187,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.0499</t>
+          <t>-0.0421</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-0.1247</t>
+          <t>-0.1072</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1409,17 +1222,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-0.0878</t>
+          <t>-0.0794</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>-0.2986</t>
+          <t>-0.2779</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1521,7 +1334,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:12 ACST</t>
+          <t>2026-05-04 07:11:43 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1708,7 +1521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:12 ACST</t>
+          <t>2026-05-04 07:11:43 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2477,7 +2290,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:12 ACST</t>
+          <t>2026-05-04 07:11:43 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2656,193 +2469,6 @@
         </is>
       </c>
       <c r="AK2" t="inlineStr">
-        <is>
-          <t>Phase 4 status was upstream_blocked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-04 06:57:12 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>flashscore:GOQASy66</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Almeria</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Mirandes</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
         <is>
           <t>Phase 4 status was upstream_blocked.</t>
         </is>
@@ -2875,7 +2501,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-04 06:57:12 ACST</t>
+          <t>2026-05-04 07:11:43 ACST</t>
         </is>
       </c>
     </row>
@@ -3031,7 +2657,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
+++ b/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
@@ -205,7 +205,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:43 ACST</t>
+          <t>2026-05-04 07:25:09 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -245,17 +245,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.0421</t>
+          <t>-0.0666</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-0.1072</t>
+          <t>-0.1598</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -280,17 +280,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-0.0794</t>
+          <t>-0.0878</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>-0.2779</t>
+          <t>-0.2986</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -315,22 +315,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.0619</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.1622</t>
+          <t>0.2199</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.1001</t>
+          <t>0.1257</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -355,7 +355,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -365,7 +365,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0619</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -392,7 +392,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:43 ACST</t>
+          <t>2026-05-04 07:25:09 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:43 ACST</t>
+          <t>2026-05-04 07:25:09 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:43 ACST</t>
+          <t>2026-05-04 07:25:09 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:43 ACST</t>
+          <t>2026-05-04 07:25:09 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1187,17 +1187,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.0421</t>
+          <t>-0.0666</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-0.1072</t>
+          <t>-0.1598</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1222,17 +1222,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-0.0794</t>
+          <t>-0.0878</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>-0.2779</t>
+          <t>-0.2986</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1257,22 +1257,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.0619</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.1622</t>
+          <t>0.2199</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.1001</t>
+          <t>0.1257</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0619</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -1334,7 +1334,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:43 ACST</t>
+          <t>2026-05-04 07:25:09 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1521,7 +1521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:43 ACST</t>
+          <t>2026-05-04 07:25:09 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2290,7 +2290,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:43 ACST</t>
+          <t>2026-05-04 07:25:09 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:11:43 ACST</t>
+          <t>2026-05-04 07:25:09 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
+++ b/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
@@ -205,7 +205,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:25:09 ACST</t>
+          <t>2026-05-04 07:34:23 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -245,17 +245,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.0666</t>
+          <t>-0.0701</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-0.1598</t>
+          <t>-0.1668</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -315,22 +315,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.0865</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.2199</t>
+          <t>0.2421</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.1257</t>
+          <t>0.1345</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -355,7 +355,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -365,7 +365,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.0865</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -392,7 +392,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:25:09 ACST</t>
+          <t>2026-05-04 07:34:23 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:25:09 ACST</t>
+          <t>2026-05-04 07:34:23 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-04 07:25:09 ACST</t>
+          <t>2026-05-04 07:34:23 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:25:09 ACST</t>
+          <t>2026-05-04 07:34:23 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1187,17 +1187,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.0666</t>
+          <t>-0.0701</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-0.1598</t>
+          <t>-0.1668</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1257,22 +1257,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.0865</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.2199</t>
+          <t>0.2421</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.1257</t>
+          <t>0.1345</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.0865</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -1334,7 +1334,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:25:09 ACST</t>
+          <t>2026-05-04 07:34:23 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1521,7 +1521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:25:09 ACST</t>
+          <t>2026-05-04 07:34:23 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2290,7 +2290,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:25:09 ACST</t>
+          <t>2026-05-04 07:34:23 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:25:09 ACST</t>
+          <t>2026-05-04 07:34:23 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
+++ b/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
@@ -205,17 +205,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:23 ACST</t>
+          <t>2026-05-04 11:09:27 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:2qevfSqS</t>
+          <t>flashscore:n1pZG14F</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -225,152 +225,152 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Austin FC</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Nottingham</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.3501</t>
+          <t/>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t/>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.0701</t>
+          <t/>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-0.1668</t>
+          <t/>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t/>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t/>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t/>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.2063</t>
+          <t/>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t/>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-0.0878</t>
+          <t/>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>-0.2986</t>
+          <t/>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t/>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t/>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t/>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.4436</t>
+          <t/>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t/>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.0865</t>
+          <t/>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.2421</t>
+          <t/>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.1345</t>
+          <t/>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t/>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>bet</t>
+          <t/>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>away</t>
+          <t/>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>bet</t>
+          <t/>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t/>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.4436</t>
+          <t/>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0865</t>
+          <t/>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t/>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -380,29 +380,29 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>bet</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Bet recommended; subject to portfolio cap.</t>
+          <t>Phase 4 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:23 ACST</t>
+          <t>2026-05-04 11:09:27 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>MLS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:n1pZG14F</t>
+          <t>flashscore:2qevfSqS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -412,17 +412,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Austin FC</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nottingham</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:23 ACST</t>
+          <t>2026-05-04 11:09:27 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:23 ACST</t>
+          <t>2026-05-04 11:09:27 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -841,22 +841,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.0018</t>
+          <t>-0.003</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.0083</t>
+          <t>-0.0136</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.0023</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1147,57 +1147,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:23 ACST</t>
+          <t>2026-05-04 11:09:27 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:2qevfSqS</t>
+          <t>flashscore:zs3PZaZa</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Austin FC</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.3501</t>
+          <t>0.3097</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.0701</t>
+          <t>-0.107</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-0.1668</t>
+          <t>-0.2567</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1217,64 +1217,64 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
+          <t>0.2084</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>-0.0857</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>-0.2914</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.4819</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.1347</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.3879</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>0.2063</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>-0.0878</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>-0.2986</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0.4436</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>2.8</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0.0865</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0.2421</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0.1345</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>20.0</t>
@@ -1297,17 +1297,17 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.4436</t>
+          <t>0.4819</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0865</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -1334,17 +1334,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:23 ACST</t>
+          <t>2026-05-04 11:09:27 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:zs3PZaZa</t>
+          <t>flashscore:rTwrFuZR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1359,347 +1359,160 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.3097</t>
+          <t>0.2111</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.107</t>
+          <t>0.0573</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-0.2567</t>
+          <t>0.3722</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>0.0677</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>16.93</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>bet</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.2192</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>-0.003</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>-0.0136</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0.2084</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>-0.0857</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>-0.2914</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.5697</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>-0.1247</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>-0.1796</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0.4819</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0.3879</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.2063</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>bet</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0.2111</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0.0573</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>16.93</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>bet</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0.4819</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
       <c r="AK3" t="inlineStr">
-        <is>
-          <t>Bet recommended; subject to portfolio cap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-04 07:34:23 ACST</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>flashscore:rTwrFuZR</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.2111</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.0573</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.3722</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0.0677</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>16.93</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0.2192</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>4.6</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0.0018</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0.0083</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0.0023</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0.5697</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>-0.1247</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>-0.1796</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0.2111</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0.0573</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>16.93</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
         <is>
           <t>Bet recommended; subject to portfolio cap.</t>
         </is>
@@ -2290,7 +2103,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:23 ACST</t>
+          <t>2026-05-04 11:09:27 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2469,6 +2282,193 @@
         </is>
       </c>
       <c r="AK2" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-04 11:09:27 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>flashscore:2qevfSqS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Austin FC</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>Phase 4 status was upstream_blocked.</t>
         </is>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-04 07:34:23 ACST</t>
+          <t>2026-05-04 11:09:27 ACST</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>56.93</t>
+          <t>36.93</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
+++ b/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
@@ -205,172 +205,172 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:27 ACST</t>
+          <t>2026-05-05 01:24:50 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:n1pZG14F</t>
+          <t>flashscore:zs3PZaZa</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nottingham</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.3097</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t/>
+          <t>2.45</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t/>
+          <t>-0.0985</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t/>
+          <t>-0.2412</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t/>
+          <t>pass</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2084</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t/>
+          <t>3.3</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t/>
+          <t>-0.0946</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t/>
+          <t>-0.3123</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t/>
+          <t>pass</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.4819</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t/>
+          <t>2.88</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.3879</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2063</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t/>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t/>
+          <t>bet</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t/>
+          <t>away</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t/>
+          <t>bet</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t/>
+          <t>2.88</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.4819</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t/>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -380,184 +380,184 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>bet</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Phase 4 status was upstream_blocked.</t>
+          <t>Bet recommended; subject to portfolio cap.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:27 ACST</t>
+          <t>2026-05-05 01:24:50 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:2qevfSqS</t>
+          <t>flashscore:rTwrFuZR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Austin FC</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2111</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t/>
+          <t>6.5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0573</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.3722</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0677</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t/>
+          <t>16.93</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t/>
+          <t>bet</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2192</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t/>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t/>
+          <t>-0.003</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t/>
+          <t>-0.0136</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t/>
+          <t>pass</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.5697</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t/>
+          <t>1.44</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t/>
+          <t>-0.1247</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t/>
+          <t>-0.1796</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t/>
+          <t>pass</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t/>
+          <t>home</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t/>
+          <t>bet</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t/>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.2111</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t/>
+          <t>0.0573</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t/>
+          <t>16.93</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -567,384 +567,10 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>upstream_blocked</t>
+          <t>bet</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
-        <is>
-          <t>Phase 4 status was upstream_blocked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-04 11:09:27 ACST</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>flashscore:zs3PZaZa</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.3097</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-0.107</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-0.2567</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0.2084</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>-0.0857</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>-0.2914</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0.4819</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0.3879</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0.2063</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0.4819</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Bet recommended; subject to portfolio cap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-05-04 11:09:27 ACST</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>flashscore:rTwrFuZR</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.2111</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.0573</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.3722</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0.0677</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>16.93</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0.2192</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>-0.003</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>-0.0136</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0.5697</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>-0.1247</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>-0.1796</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0.2111</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0.0573</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>16.93</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
         <is>
           <t>Bet recommended; subject to portfolio cap.</t>
         </is>
@@ -1147,7 +773,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:27 ACST</t>
+          <t>2026-05-05 01:24:50 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1187,17 +813,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.107</t>
+          <t>-0.0985</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-0.2567</t>
+          <t>-0.2412</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1222,17 +848,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-0.0857</t>
+          <t>-0.0946</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>-0.2914</t>
+          <t>-0.3123</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1334,7 +960,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:27 ACST</t>
+          <t>2026-05-05 01:24:50 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2100,380 +1726,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-04 11:09:27 ACST</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>flashscore:n1pZG14F</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Chelsea</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Nottingham</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Phase 4 status was upstream_blocked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-04 11:09:27 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>flashscore:2qevfSqS</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Austin FC</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>St. Louis City</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Phase 4 status was upstream_blocked.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -2501,7 +1753,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-04 11:09:27 ACST</t>
+          <t>2026-05-05 01:24:50 ACST</t>
         </is>
       </c>
     </row>
@@ -2657,7 +1909,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
+++ b/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
@@ -205,7 +205,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:50 ACST</t>
+          <t>2026-05-05 01:28:49 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -392,7 +392,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:50 ACST</t>
+          <t>2026-05-05 01:28:49 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -773,7 +773,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:50 ACST</t>
+          <t>2026-05-05 01:28:49 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -960,7 +960,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:50 ACST</t>
+          <t>2026-05-05 01:28:49 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-05 01:24:50 ACST</t>
+          <t>2026-05-05 01:28:49 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
+++ b/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
@@ -205,172 +205,172 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-05 01:28:49 ACST</t>
+          <t>2026-05-06 01:40:49 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:zs3PZaZa</t>
+          <t>16072838</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Roda JC Kerkrade</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.3097</t>
+          <t/>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t/>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.0985</t>
+          <t/>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-0.2412</t>
+          <t/>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t/>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t/>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t/>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.2084</t>
+          <t/>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t/>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-0.0946</t>
+          <t/>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>-0.3123</t>
+          <t/>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t/>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t/>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t/>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.4819</t>
+          <t/>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t/>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t/>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.3879</t>
+          <t/>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.2063</t>
+          <t/>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t/>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>bet</t>
+          <t/>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>away</t>
+          <t/>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>bet</t>
+          <t/>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t/>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.4819</t>
+          <t/>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t/>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t/>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -380,199 +380,760 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>bet</t>
+          <t>upstream_blocked</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Bet recommended; subject to portfolio cap.</t>
+          <t>Phase 4 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-05 01:28:49 ACST</t>
+          <t>2026-05-06 01:40:49 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:rTwrFuZR</t>
+          <t>16115678</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>RKC Waalwijk</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:40:49 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>15632635</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>04:30</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.2111</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.0573</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.3722</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0.0677</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>16.93</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0.2192</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>-0.003</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>-0.0136</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0.5697</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>-0.1247</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>-0.1796</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0.2111</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0.0573</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>16.93</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Bet recommended; subject to portfolio cap.</t>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:40:49 ACST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>16115794</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Almere City FC</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>De Graafschap</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:40:49 ACST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>15632634</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>FC Bayern München</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Paris Saint-Germain</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
         </is>
       </c>
     </row>
@@ -770,380 +1331,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-05-05 01:28:49 ACST</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>LaLiga</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>flashscore:zs3PZaZa</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.3097</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-0.0985</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>-0.2412</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0.2084</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>-0.0946</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>-0.3123</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0.4819</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0.3879</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0.2063</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0.4819</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Bet recommended; subject to portfolio cap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-05 01:28:49 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>flashscore:rTwrFuZR</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Everton</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.2111</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.0573</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.3722</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0.0677</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>16.93</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0.2192</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>-0.003</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>-0.0136</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0.5697</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>-0.1247</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>-0.1796</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0.2111</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0.0573</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>16.93</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>bet</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Bet recommended; subject to portfolio cap.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1726,6 +1913,941 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:40:49 ACST</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>16072838</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Roda JC Kerkrade</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>RKC Waalwijk</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:40:49 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>16115678</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>RKC Waalwijk</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Willem II Tilburg</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:40:49 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>15632635</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:40:49 ACST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Eredivisie</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>16115794</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Almere City FC</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>De Graafschap</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:40:49 ACST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>15632634</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>FC Bayern München</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Paris Saint-Germain</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1753,7 +2875,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-05 01:28:49 ACST</t>
+          <t>2026-05-06 01:40:49 ACST</t>
         </is>
       </c>
     </row>
@@ -1837,7 +2959,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>36.93</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1873,7 +2995,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1909,7 +3031,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1921,7 +3043,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Phase 6 will settle results once matches are FT.</t>
+          <t>No bets today; revisit on next data refresh.</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
+++ b/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
@@ -205,7 +205,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:49 ACST</t>
+          <t>2026-05-07 01:36:58 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -392,7 +392,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:49 ACST</t>
+          <t>2026-05-07 01:36:58 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -402,12 +402,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16115678</t>
+          <t>16115794</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -417,12 +417,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City FC</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:49 ACST</t>
+          <t>2026-05-07 01:36:58 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -589,12 +589,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15632635</t>
+          <t>15632634</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -604,12 +604,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>FC Bayern München</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Paris Saint-Germain</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -766,37 +766,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:49 ACST</t>
+          <t>2026-05-07 01:36:58 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16115794</t>
+          <t>14065245</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>02:15</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Almere City FC</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -953,185 +953,933 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:49 ACST</t>
+          <t>2026-05-07 01:36:58 ACST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15632634</t>
+          <t>14064514</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>RC Lens</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:58 ACST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>16116799</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>04:30</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>FC Bayern München</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Paris Saint-Germain</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Millwall</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>upstream_blocked</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr">
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:58 ACST</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>14083568</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Levante UD</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:58 ACST</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>16116800</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:58 ACST</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>14024024</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Liverpool FC</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>Phase 4 status was upstream_blocked.</t>
         </is>
@@ -1916,7 +2664,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:49 ACST</t>
+          <t>2026-05-07 01:36:58 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2103,7 +2851,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:49 ACST</t>
+          <t>2026-05-07 01:36:58 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2113,12 +2861,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16115678</t>
+          <t>16115794</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2128,12 +2876,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City FC</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Willem II Tilburg</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2290,7 +3038,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:49 ACST</t>
+          <t>2026-05-07 01:36:58 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2300,12 +3048,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15632635</t>
+          <t>15632634</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2315,12 +3063,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>FC Bayern München</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Paris Saint-Germain</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2477,37 +3225,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:49 ACST</t>
+          <t>2026-05-07 01:36:58 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Eredivisie</t>
+          <t>Bundesliga</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16115794</t>
+          <t>14065245</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>02:15</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Almere City FC</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2664,185 +3412,933 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:49 ACST</t>
+          <t>2026-05-07 01:36:58 ACST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15632634</t>
+          <t>14064514</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>RC Lens</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:58 ACST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>16116799</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>04:30</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>FC Bayern München</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Paris Saint-Germain</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Millwall</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>upstream_blocked</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr">
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:58 ACST</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>14083568</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Levante UD</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:58 ACST</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>16116800</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-07 01:36:58 ACST</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>14024024</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Liverpool FC</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>Phase 4 status was upstream_blocked.</t>
         </is>
@@ -2875,7 +4371,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-06 01:40:49 ACST</t>
+          <t>2026-05-07 01:36:58 ACST</t>
         </is>
       </c>
     </row>
@@ -3031,7 +4527,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
+++ b/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
@@ -205,17 +205,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:vyaxjXte</t>
+          <t>flashscore:YH84GNJi</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -225,17 +225,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ath. Bilbao</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -392,17 +392,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:n12plBB7</t>
+          <t>flashscore:nmmS8WHr</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -412,17 +412,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atl. Madrid</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -579,17 +579,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>flashscore:0OhvAhYQ</t>
+          <t>flashscore:h0IS6Ane</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -766,17 +766,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>flashscore:K8ZA4Wel</t>
+          <t>flashscore:prPnPy9r</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -786,17 +786,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -953,17 +953,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>flashscore:YFVo6qXh</t>
+          <t>flashscore:IXv8WJG8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -973,17 +973,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1140,17 +1140,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>flashscore:C0sw852t</t>
+          <t>flashscore:r1cGQTSk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>flashscore:llRR0leD</t>
+          <t>flashscore:OhrGQlpm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,17 +1347,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1514,17 +1514,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>flashscore:ttZg4N15</t>
+          <t>flashscore:xbwdLg87</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1534,17 +1534,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>flashscore:hMXI2AQ0</t>
+          <t>flashscore:QcrGUcoL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vallecano</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1888,17 +1888,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>flashscore:YH84GNJi</t>
+          <t>flashscore:IeNfNFwe</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1908,17 +1908,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Paris FC</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>flashscore:nmmS8WHr</t>
+          <t>flashscore:44Vsqc0E</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2095,17 +2095,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2262,17 +2262,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>flashscore:h0IS6Ane</t>
+          <t>flashscore:SduXBE3E</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2282,17 +2282,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2449,17 +2449,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>flashscore:prPnPy9r</t>
+          <t>flashscore:vyaxjXte</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2469,17 +2469,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Ath. Bilbao</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2636,17 +2636,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>flashscore:IXv8WJG8</t>
+          <t>flashscore:n12plBB7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2656,17 +2656,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Atl. Madrid</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2823,17 +2823,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>flashscore:r1cGQTSk</t>
+          <t>flashscore:0OhvAhYQ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2843,17 +2843,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -3010,17 +3010,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>flashscore:OhrGQlpm</t>
+          <t>flashscore:K8ZA4Wel</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3030,17 +3030,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -3197,17 +3197,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>flashscore:xbwdLg87</t>
+          <t>flashscore:YFVo6qXh</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3217,17 +3217,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3384,17 +3384,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>flashscore:z9FNO7c2</t>
+          <t>flashscore:C0sw852t</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3404,17 +3404,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Oviedo</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Alaves</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3571,17 +3571,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>flashscore:QcrGUcoL</t>
+          <t>flashscore:llRR0leD</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3591,17 +3591,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3758,17 +3758,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>flashscore:IeNfNFwe</t>
+          <t>flashscore:ttZg4N15</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3778,17 +3778,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paris FC</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3945,17 +3945,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>flashscore:44Vsqc0E</t>
+          <t>flashscore:hMXI2AQ0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3965,17 +3965,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Vallecano</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -4132,17 +4132,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>flashscore:SduXBE3E</t>
+          <t>flashscore:z9FNO7c2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4152,17 +4152,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -4319,7 +4319,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5282,17 +5282,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:vyaxjXte</t>
+          <t>flashscore:YH84GNJi</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -5302,17 +5302,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ath. Bilbao</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -5469,17 +5469,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:n12plBB7</t>
+          <t>flashscore:nmmS8WHr</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -5489,17 +5489,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atl. Madrid</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -5656,17 +5656,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Serie A</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>flashscore:0OhvAhYQ</t>
+          <t>flashscore:h0IS6Ane</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -5676,17 +5676,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -5843,17 +5843,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>flashscore:K8ZA4Wel</t>
+          <t>flashscore:prPnPy9r</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -5863,17 +5863,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6030,17 +6030,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>flashscore:YFVo6qXh</t>
+          <t>flashscore:IXv8WJG8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -6050,17 +6050,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -6217,17 +6217,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>flashscore:C0sw852t</t>
+          <t>flashscore:r1cGQTSk</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -6237,17 +6237,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -6404,17 +6404,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>flashscore:llRR0leD</t>
+          <t>flashscore:OhrGQlpm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -6424,17 +6424,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -6591,17 +6591,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>flashscore:ttZg4N15</t>
+          <t>flashscore:xbwdLg87</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -6611,17 +6611,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -6778,17 +6778,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>flashscore:hMXI2AQ0</t>
+          <t>flashscore:QcrGUcoL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -6798,17 +6798,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vallecano</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -6965,17 +6965,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>flashscore:YH84GNJi</t>
+          <t>flashscore:IeNfNFwe</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -6985,17 +6985,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Paris FC</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -7152,17 +7152,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>flashscore:nmmS8WHr</t>
+          <t>flashscore:44Vsqc0E</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -7172,17 +7172,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -7339,17 +7339,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>flashscore:h0IS6Ane</t>
+          <t>flashscore:SduXBE3E</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -7359,17 +7359,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -7526,17 +7526,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>flashscore:prPnPy9r</t>
+          <t>flashscore:vyaxjXte</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -7546,17 +7546,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Ath. Bilbao</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -7713,17 +7713,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>flashscore:IXv8WJG8</t>
+          <t>flashscore:n12plBB7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -7733,17 +7733,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Atl. Madrid</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -7900,17 +7900,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>flashscore:r1cGQTSk</t>
+          <t>flashscore:0OhvAhYQ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -7920,17 +7920,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -8087,17 +8087,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>flashscore:OhrGQlpm</t>
+          <t>flashscore:K8ZA4Wel</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -8107,17 +8107,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -8274,17 +8274,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>flashscore:xbwdLg87</t>
+          <t>flashscore:YFVo6qXh</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -8294,17 +8294,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -8461,17 +8461,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>flashscore:z9FNO7c2</t>
+          <t>flashscore:C0sw852t</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -8481,17 +8481,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Oviedo</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Alaves</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -8648,17 +8648,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>flashscore:QcrGUcoL</t>
+          <t>flashscore:llRR0leD</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -8668,17 +8668,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -8835,17 +8835,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>flashscore:IeNfNFwe</t>
+          <t>flashscore:ttZg4N15</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -8855,17 +8855,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paris FC</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -9022,17 +9022,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ligue 1</t>
+          <t>LaLiga</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>flashscore:44Vsqc0E</t>
+          <t>flashscore:hMXI2AQ0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -9042,17 +9042,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Vallecano</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -9209,17 +9209,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LaLiga</t>
+          <t>Ligue 1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>flashscore:SduXBE3E</t>
+          <t>flashscore:z9FNO7c2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -9229,17 +9229,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -9396,7 +9396,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-18 04:09:11 ACST</t>
+          <t>2026-05-18 05:57:50 ACST</t>
         </is>
       </c>
     </row>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-18 04:06:59 ACST</t>
+          <t>2026-05-18 05:06:52 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
+++ b/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
@@ -205,7 +205,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 09:54:49 ACST</t>
+          <t>2026-05-18 13:54:26 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -215,7 +215,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:lnSvmTkR</t>
+          <t>flashscore:rZdvkkLE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -225,17 +225,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -392,7 +392,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 09:54:49 ACST</t>
+          <t>2026-05-18 13:54:26 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -402,7 +402,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:rZdvkkLE</t>
+          <t>flashscore:lnSvmTkR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -417,12 +417,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 09:54:49 ACST</t>
+          <t>2026-05-18 13:54:26 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1542,7 +1542,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 09:54:49 ACST</t>
+          <t>2026-05-18 13:54:26 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:lnSvmTkR</t>
+          <t>flashscore:rZdvkkLE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1562,17 +1562,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1729,7 +1729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 09:54:49 ACST</t>
+          <t>2026-05-18 13:54:26 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:rZdvkkLE</t>
+          <t>flashscore:lnSvmTkR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1754,12 +1754,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1916,7 +1916,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 09:54:49 ACST</t>
+          <t>2026-05-18 13:54:26 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-18 09:54:49 ACST</t>
+          <t>2026-05-18 13:54:26 ACST</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-18 09:10:02 ACST</t>
+          <t>2026-05-18 12:12:56 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
+++ b/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
@@ -205,7 +205,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 13:54:26 ACST</t>
+          <t>2026-05-18 17:54:32 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -392,7 +392,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 13:54:26 ACST</t>
+          <t>2026-05-18 17:54:32 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 13:54:26 ACST</t>
+          <t>2026-05-18 17:54:32 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1542,7 +1542,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 13:54:26 ACST</t>
+          <t>2026-05-18 17:54:32 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1729,7 +1729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18 13:54:26 ACST</t>
+          <t>2026-05-18 17:54:32 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1916,7 +1916,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18 13:54:26 ACST</t>
+          <t>2026-05-18 17:54:32 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-18 13:54:26 ACST</t>
+          <t>2026-05-18 17:54:32 ACST</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-18 12:12:56 ACST</t>
+          <t>2026-05-18 13:54:28 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
+++ b/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
@@ -205,37 +205,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 17:54:32 ACST</t>
+          <t>2026-05-19 01:54:17 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:rZdvkkLE</t>
+          <t>flashscore:Gxt6zm15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -384,380 +384,6 @@
         </is>
       </c>
       <c r="AK2" t="inlineStr">
-        <is>
-          <t>Phase 4 status was upstream_blocked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-18 17:54:32 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>flashscore:lnSvmTkR</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Nashville SC</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Phase 4 status was upstream_blocked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-18 17:54:32 ACST</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>flashscore:Gxt6zm15</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Arsenal</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Burnley</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
         <is>
           <t>Phase 4 status was upstream_blocked.</t>
         </is>
@@ -1542,37 +1168,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18 17:54:32 ACST</t>
+          <t>2026-05-19 01:54:17 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MLS</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:rZdvkkLE</t>
+          <t>flashscore:Gxt6zm15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1721,380 +1347,6 @@
         </is>
       </c>
       <c r="AK2" t="inlineStr">
-        <is>
-          <t>Phase 4 status was upstream_blocked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-18 17:54:32 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>flashscore:lnSvmTkR</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Nashville SC</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Phase 4 status was upstream_blocked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-18 17:54:32 ACST</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>flashscore:Gxt6zm15</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>04:30</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Arsenal</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Burnley</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
         <is>
           <t>Phase 4 status was upstream_blocked.</t>
         </is>
@@ -2127,7 +1379,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-18 17:54:32 ACST</t>
+          <t>2026-05-19 01:54:17 ACST</t>
         </is>
       </c>
     </row>
@@ -2175,7 +1427,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-18 13:54:28 ACST</t>
+          <t>2026-05-19 01:31:07 ACST</t>
         </is>
       </c>
     </row>
@@ -2295,7 +1547,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
+++ b/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
@@ -205,7 +205,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-19 01:54:17 ACST</t>
+          <t>2026-05-19 17:59:55 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -215,27 +215,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:Gxt6zm15</t>
+          <t>flashscore:rkXMW40U</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -384,6 +384,193 @@
         </is>
       </c>
       <c r="AK2" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:59:55 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>flashscore:Uu6uknGb</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>04:45</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tottenham</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>Phase 4 status was upstream_blocked.</t>
         </is>
@@ -1168,7 +1355,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-19 01:54:17 ACST</t>
+          <t>2026-05-19 17:59:55 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1178,27 +1365,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:Gxt6zm15</t>
+          <t>flashscore:rkXMW40U</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1347,6 +1534,193 @@
         </is>
       </c>
       <c r="AK2" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:59:55 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>flashscore:Uu6uknGb</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>04:45</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tottenham</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>Phase 4 status was upstream_blocked.</t>
         </is>
@@ -1379,7 +1753,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-19 01:54:17 ACST</t>
+          <t>2026-05-19 17:59:55 ACST</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1801,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-19 01:31:07 ACST</t>
+          <t>2026-05-19 17:56:58 ACST</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1921,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
+++ b/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
@@ -205,7 +205,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:59:55 ACST</t>
+          <t>2026-05-20 01:56:56 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -392,7 +392,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-19 17:59:55 ACST</t>
+          <t>2026-05-20 01:56:56 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1355,7 +1355,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:59:55 ACST</t>
+          <t>2026-05-20 01:56:56 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1542,7 +1542,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-19 17:59:55 ACST</t>
+          <t>2026-05-20 01:56:56 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:59:55 ACST</t>
+          <t>2026-05-20 01:56:56 ACST</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-19 17:56:58 ACST</t>
+          <t>2026-05-19 19:01:17 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
+++ b/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
@@ -205,7 +205,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-20 01:56:56 ACST</t>
+          <t>2026-05-20 05:56:08 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -215,7 +215,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:rkXMW40U</t>
+          <t>flashscore:Uu6uknGb</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -225,17 +225,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -392,7 +392,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-20 01:56:56 ACST</t>
+          <t>2026-05-20 05:56:08 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -402,7 +402,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:Uu6uknGb</t>
+          <t>flashscore:rkXMW40U</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -412,17 +412,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1355,7 +1355,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-20 01:56:56 ACST</t>
+          <t>2026-05-20 05:56:08 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:rkXMW40U</t>
+          <t>flashscore:Uu6uknGb</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1375,17 +1375,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1542,7 +1542,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-20 01:56:56 ACST</t>
+          <t>2026-05-20 05:56:08 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:Uu6uknGb</t>
+          <t>flashscore:rkXMW40U</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1562,17 +1562,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Bournemouth</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-20 01:56:56 ACST</t>
+          <t>2026-05-20 05:56:08 ACST</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-19 19:01:17 ACST</t>
+          <t>2026-05-20 05:34:41 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
+++ b/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
@@ -205,37 +205,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-20 05:56:08 ACST</t>
+          <t>2026-05-20 09:58:04 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:Uu6uknGb</t>
+          <t>thesportsdb:2475105</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>02:15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -392,37 +392,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-20 05:56:08 ACST</t>
+          <t>2026-05-20 09:58:04 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:rkXMW40U</t>
+          <t>thesportsdb:2475106</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -571,6 +571,754 @@
         </is>
       </c>
       <c r="AK3" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:58:04 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>thesportsdb:2265408</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:58:04 ACST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>thesportsdb:2279766</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:58:04 ACST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>thesportsdb:2279764</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Deportivo Alavés</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:58:04 ACST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>thesportsdb:2279765</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
         <is>
           <t>Phase 4 status was upstream_blocked.</t>
         </is>
@@ -1355,37 +2103,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-20 05:56:08 ACST</t>
+          <t>2026-05-20 09:58:04 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:Uu6uknGb</t>
+          <t>thesportsdb:2475105</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>02:15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1542,37 +2290,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-20 05:56:08 ACST</t>
+          <t>2026-05-20 09:58:04 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>Eredivisie</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:rkXMW40U</t>
+          <t>thesportsdb:2475106</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1721,6 +2469,754 @@
         </is>
       </c>
       <c r="AK3" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:58:04 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>thesportsdb:2265408</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:58:04 ACST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>thesportsdb:2279766</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:58:04 ACST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>thesportsdb:2279764</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Deportivo Alavés</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:58:04 ACST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>thesportsdb:2279765</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
         <is>
           <t>Phase 4 status was upstream_blocked.</t>
         </is>
@@ -1753,7 +3249,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-20 05:56:08 ACST</t>
+          <t>2026-05-20 09:58:04 ACST</t>
         </is>
       </c>
     </row>
@@ -1801,7 +3297,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-20 05:34:41 ACST</t>
+          <t>2026-05-20 09:41:56 ACST</t>
         </is>
       </c>
     </row>
@@ -1921,7 +3417,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
+++ b/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
@@ -205,17 +205,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:45 ACST</t>
+          <t>2026-05-21 03:43:10 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Eliteserien</t>
+          <t>Allsvenskan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:v3i3qEfD</t>
+          <t>flashscore:rJKJ2MZP</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -225,17 +225,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bodo/Glimt</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -392,17 +392,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:45 ACST</t>
+          <t>2026-05-21 03:43:10 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>Eliteserien</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:rJKJ2MZP</t>
+          <t>flashscore:YobepuNG</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -417,12 +417,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Lilleström</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:45 ACST</t>
+          <t>2026-05-21 03:43:10 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>flashscore:YobepuNG</t>
+          <t>flashscore:0A1Nl9Wh</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>03:30</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lilleström</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:45 ACST</t>
+          <t>2026-05-21 03:43:10 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>flashscore:0A1Nl9Wh</t>
+          <t>flashscore:v3i3qEfD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -786,17 +786,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Bodo/Glimt</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1729,17 +1729,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:45 ACST</t>
+          <t>2026-05-21 03:43:10 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Eliteserien</t>
+          <t>Allsvenskan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:v3i3qEfD</t>
+          <t>flashscore:rJKJ2MZP</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1749,17 +1749,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bodo/Glimt</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1916,17 +1916,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:45 ACST</t>
+          <t>2026-05-21 03:43:10 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>Eliteserien</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:rJKJ2MZP</t>
+          <t>flashscore:YobepuNG</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Lilleström</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2103,7 +2103,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:45 ACST</t>
+          <t>2026-05-21 03:43:10 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>flashscore:YobepuNG</t>
+          <t>flashscore:0A1Nl9Wh</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2123,17 +2123,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>03:30</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lilleström</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2290,7 +2290,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:45 ACST</t>
+          <t>2026-05-21 03:43:10 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>flashscore:0A1Nl9Wh</t>
+          <t>flashscore:v3i3qEfD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2310,17 +2310,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Bodo/Glimt</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21 01:56:45 ACST</t>
+          <t>2026-05-21 03:43:10 ACST</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-21 01:54:09 ACST</t>
+          <t>2026-05-21 02:40:21 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
+++ b/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
@@ -205,7 +205,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 03:43:10 ACST</t>
+          <t>2026-05-21 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -225,7 +225,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -392,7 +392,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-21 03:43:10 ACST</t>
+          <t>2026-05-21 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -402,7 +402,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:YobepuNG</t>
+          <t>flashscore:0A1Nl9Wh</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -412,17 +412,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lilleström</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-21 03:43:10 ACST</t>
+          <t>2026-05-21 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>flashscore:0A1Nl9Wh</t>
+          <t>flashscore:YobepuNG</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Lilleström</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-21 03:43:10 ACST</t>
+          <t>2026-05-21 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1729,7 +1729,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 03:43:10 ACST</t>
+          <t>2026-05-21 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1916,7 +1916,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-21 03:43:10 ACST</t>
+          <t>2026-05-21 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:YobepuNG</t>
+          <t>flashscore:0A1Nl9Wh</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1936,17 +1936,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lilleström</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2103,7 +2103,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-21 03:43:10 ACST</t>
+          <t>2026-05-21 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>flashscore:0A1Nl9Wh</t>
+          <t>flashscore:YobepuNG</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2123,17 +2123,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Lilleström</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2290,7 +2290,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-21 03:43:10 ACST</t>
+          <t>2026-05-21 05:57:50 ACST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21 03:43:10 ACST</t>
+          <t>2026-05-21 05:57:50 ACST</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-21 02:40:21 ACST</t>
+          <t>2026-05-21 05:54:42 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
+++ b/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
@@ -205,7 +205,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 05:57:50 ACST</t>
+          <t>2026-05-21 18:08:48 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -215,27 +215,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:rJKJ2MZP</t>
+          <t>flashscore:zHabevSa</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Mjallby</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -384,567 +384,6 @@
         </is>
       </c>
       <c r="AK2" t="inlineStr">
-        <is>
-          <t>Phase 4 status was upstream_blocked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-21 05:57:50 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Eliteserien</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>flashscore:0A1Nl9Wh</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Aalesund</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Brann</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Phase 4 status was upstream_blocked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-21 05:57:50 ACST</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Eliteserien</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>flashscore:YobepuNG</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Lilleström</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Kristiansund</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Phase 4 status was upstream_blocked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-05-21 05:57:50 ACST</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Eliteserien</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>flashscore:v3i3qEfD</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Bodo/Glimt</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
         <is>
           <t>Phase 4 status was upstream_blocked.</t>
         </is>
@@ -1729,7 +1168,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 05:57:50 ACST</t>
+          <t>2026-05-21 18:08:48 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1739,27 +1178,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:rJKJ2MZP</t>
+          <t>flashscore:zHabevSa</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Mjallby</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1908,567 +1347,6 @@
         </is>
       </c>
       <c r="AK2" t="inlineStr">
-        <is>
-          <t>Phase 4 status was upstream_blocked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-21 05:57:50 ACST</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Eliteserien</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>flashscore:0A1Nl9Wh</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Aalesund</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Brann</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Phase 4 status was upstream_blocked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-21 05:57:50 ACST</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Eliteserien</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>flashscore:YobepuNG</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Lilleström</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Kristiansund</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Phase 4 status was upstream_blocked.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-05-21 05:57:50 ACST</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Eliteserien</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>flashscore:v3i3qEfD</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Bodo/Glimt</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>upstream_blocked</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
         <is>
           <t>Phase 4 status was upstream_blocked.</t>
         </is>
@@ -2501,7 +1379,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21 05:57:50 ACST</t>
+          <t>2026-05-21 18:08:48 ACST</t>
         </is>
       </c>
     </row>
@@ -2549,7 +1427,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-21 05:54:42 ACST</t>
+          <t>2026-05-21 18:02:59 ACST</t>
         </is>
       </c>
     </row>
@@ -2669,7 +1547,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
+++ b/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
@@ -205,7 +205,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:08:48 ACST</t>
+          <t>2026-05-21 18:22:40 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1168,7 +1168,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:08:48 ACST</t>
+          <t>2026-05-21 18:22:40 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:08:48 ACST</t>
+          <t>2026-05-21 18:22:40 ACST</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-21 18:02:59 ACST</t>
+          <t>2026-05-21 18:08:59 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
+++ b/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
@@ -205,7 +205,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:22:40 ACST</t>
+          <t>2026-05-22 01:59:19 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1168,7 +1168,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:22:40 ACST</t>
+          <t>2026-05-22 01:59:19 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-21 18:22:40 ACST</t>
+          <t>2026-05-22 01:59:19 ACST</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-21 18:08:59 ACST</t>
+          <t>2026-05-22 01:30:48 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
+++ b/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
@@ -205,7 +205,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 01:59:19 ACST</t>
+          <t>2026-05-22 04:29:40 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -225,7 +225,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1168,7 +1168,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 01:59:19 ACST</t>
+          <t>2026-05-22 04:29:40 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22 01:59:19 ACST</t>
+          <t>2026-05-22 04:29:40 ACST</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-22 01:30:48 ACST</t>
+          <t>2026-05-22 03:28:55 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
+++ b/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
@@ -205,185 +205,559 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 04:29:40 ACST</t>
+          <t>2026-05-22 17:57:58 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>J1 League</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>flashscore:fXvLSp0T</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Machida</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Urawa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-22 17:57:58 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>flashscore:zHabevSa</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Elfsborg</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Mjallby</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>flashscore:l6SULOIj</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Djurgarden</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Brommapojkarna</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>upstream_blocked</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-22 17:57:58 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>flashscore:ln2VQVwR</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>Phase 4 status was upstream_blocked.</t>
         </is>
@@ -1168,185 +1542,559 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 04:29:40 ACST</t>
+          <t>2026-05-22 17:57:58 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>J1 League</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>flashscore:fXvLSp0T</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Machida</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Urawa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-22 17:57:58 ACST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>flashscore:zHabevSa</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>FT</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Elfsborg</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Mjallby</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>flashscore:l6SULOIj</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Djurgarden</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Brommapojkarna</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>upstream_blocked</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-22 17:57:58 ACST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>flashscore:ln2VQVwR</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>Phase 4 status was upstream_blocked.</t>
         </is>
@@ -1379,7 +2127,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22 04:29:40 ACST</t>
+          <t>2026-05-22 17:57:58 ACST</t>
         </is>
       </c>
     </row>
@@ -1427,7 +2175,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-22 03:28:55 ACST</t>
+          <t>2026-05-22 17:25:45 ACST</t>
         </is>
       </c>
     </row>
@@ -1547,7 +2295,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
+++ b/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
@@ -205,7 +205,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 17:57:58 ACST</t>
+          <t>2026-05-22 18:59:47 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -392,7 +392,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 17:57:58 ACST</t>
+          <t>2026-05-22 18:59:47 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22 17:57:58 ACST</t>
+          <t>2026-05-22 18:59:47 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1542,7 +1542,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 17:57:58 ACST</t>
+          <t>2026-05-22 18:59:47 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1729,7 +1729,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 17:57:58 ACST</t>
+          <t>2026-05-22 18:59:47 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1916,7 +1916,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22 17:57:58 ACST</t>
+          <t>2026-05-22 18:59:47 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22 17:57:58 ACST</t>
+          <t>2026-05-22 18:59:47 ACST</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-22 17:25:45 ACST</t>
+          <t>2026-05-22 18:14:10 ACST</t>
         </is>
       </c>
     </row>

--- a/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
+++ b/docs/agent-system/outputs/Phase5_Value_Risk.xlsx
@@ -205,37 +205,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 18:59:47 ACST</t>
+          <t>2026-06-05 19:29:23 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>J1 League</t>
+          <t>International Friendly Games</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:fXvLSp0T</t>
+          <t>flashscore:EsE6FP8c</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Machida</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Urawa</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -392,37 +392,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 18:59:47 ACST</t>
+          <t>2026-06-05 19:29:23 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>International Friendly Games</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:l6SULOIj</t>
+          <t>flashscore:AqnFNaI5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Djurgarden</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -579,37 +579,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22 18:59:47 ACST</t>
+          <t>2026-06-05 19:29:23 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>International Friendly Games</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>flashscore:ln2VQVwR</t>
+          <t>flashscore:f55NQIsS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -758,6 +758,3372 @@
         </is>
       </c>
       <c r="AK4" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>flashscore:WCykuuhU</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>flashscore:A7YX1Ha6</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Botswana</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>flashscore:j1djEBZR</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>flashscore:MHMpxPfo</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Liberia</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Benin</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>flashscore:b1x9Omno</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>flashscore:UTlT8H3E</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>flashscore:GCkooKhS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tajikistan</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>flashscore:x0ey9SdL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Belarus</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>flashscore:lIwBomFD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>flashscore:G4u3m9p1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>flashscore:Cv3iCkuq</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Moldova</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>flashscore:fJz9NRBE</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Burkina Faso</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>flashscore:rPCLHBHL</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>San Marino</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>flashscore:bZVLx0FO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>03:15</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>flashscore:jDnBGlak</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Azerbaijan</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>flashscore:fNtF7Ai4</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Benin</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Niger</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>flashscore:8xq71Zel</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Central Africa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Togo</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>flashscore:WjtZbjct</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Mauritania</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
         <is>
           <t>Phase 4 status was upstream_blocked.</t>
         </is>
@@ -1542,37 +4908,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 18:59:47 ACST</t>
+          <t>2026-06-05 19:29:23 ACST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>J1 League</t>
+          <t>International Friendly Games</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>flashscore:fXvLSp0T</t>
+          <t>flashscore:EsE6FP8c</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Machida</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Urawa</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1729,37 +5095,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 18:59:47 ACST</t>
+          <t>2026-06-05 19:29:23 ACST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>International Friendly Games</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>flashscore:l6SULOIj</t>
+          <t>flashscore:AqnFNaI5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Djurgarden</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1916,37 +5282,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22 18:59:47 ACST</t>
+          <t>2026-06-05 19:29:23 ACST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Serie A</t>
+          <t>International Friendly Games</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>flashscore:ln2VQVwR</t>
+          <t>flashscore:f55NQIsS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2095,6 +5461,3372 @@
         </is>
       </c>
       <c r="AK4" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>flashscore:WCykuuhU</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>flashscore:A7YX1Ha6</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Botswana</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>flashscore:j1djEBZR</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>flashscore:MHMpxPfo</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Liberia</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Benin</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>flashscore:b1x9Omno</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>flashscore:UTlT8H3E</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>flashscore:GCkooKhS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tajikistan</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>flashscore:x0ey9SdL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Belarus</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Syria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>flashscore:lIwBomFD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>flashscore:G4u3m9p1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>flashscore:Cv3iCkuq</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Moldova</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>flashscore:fJz9NRBE</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Burkina Faso</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>flashscore:rPCLHBHL</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>San Marino</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>flashscore:bZVLx0FO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>03:15</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>flashscore:jDnBGlak</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Azerbaijan</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>flashscore:fNtF7Ai4</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Benin</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Niger</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>flashscore:8xq71Zel</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Central Africa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Togo</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Phase 4 status was upstream_blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:29:23 ACST</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>International Friendly Games</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>flashscore:WjtZbjct</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Angola</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Mauritania</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>upstream_blocked</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
         <is>
           <t>Phase 4 status was upstream_blocked.</t>
         </is>
@@ -2127,7 +8859,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22 18:59:47 ACST</t>
+          <t>2026-06-05 19:29:23 ACST</t>
         </is>
       </c>
     </row>
@@ -2175,7 +8907,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-22 18:14:10 ACST</t>
+          <t>2026-06-05 19:04:56 ACST</t>
         </is>
       </c>
     </row>
@@ -2295,7 +9027,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
     </row>
